--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N84_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.30166843853732</v>
+        <v>9.474021121262314</v>
       </c>
       <c r="D2" t="n">
-        <v>76.9311261573428</v>
+        <v>12.50130800056821</v>
       </c>
       <c r="E2" t="n">
-        <v>20.90900005403769</v>
+        <v>3.397712508781126</v>
       </c>
       <c r="F2" t="n">
-        <v>10.62675859822271</v>
+        <v>1.726848272211192</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.54947309793891</v>
+        <v>12.43928937841507</v>
       </c>
       <c r="D3" t="n">
-        <v>66.41851689107388</v>
+        <v>10.79300899479951</v>
       </c>
       <c r="E3" t="n">
-        <v>20.90900005403769</v>
+        <v>3.397712508781126</v>
       </c>
       <c r="F3" t="n">
-        <v>10.62675859822271</v>
+        <v>1.726848272211192</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>84.88217759828115</v>
+        <v>13.79335385972069</v>
       </c>
       <c r="D4" t="n">
-        <v>76.8898427881348</v>
+        <v>12.49459945307191</v>
       </c>
       <c r="E4" t="n">
-        <v>20.90900005403769</v>
+        <v>3.397712508781126</v>
       </c>
       <c r="F4" t="n">
-        <v>10.62675859822271</v>
+        <v>1.726848272211192</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.36323122556762</v>
+        <v>4.934025074154739</v>
       </c>
       <c r="D5" t="n">
-        <v>50.9536115818124</v>
+        <v>8.279961882044514</v>
       </c>
       <c r="E5" t="n">
-        <v>20.90900005403769</v>
+        <v>3.397712508781126</v>
       </c>
       <c r="F5" t="n">
-        <v>10.62675859822271</v>
+        <v>1.726848272211192</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
